--- a/output/graficos_regionales_sexo_edad/plot_historia_nacional_o_ocup_a_2021_nacional.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_historia_nacional_o_ocup_a_2021_nacional.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t xml:space="preserve">Año</t>
   </si>
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 09:45</t>
+    <t xml:space="preserve">2026-09-18 09:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -83,9 +83,6 @@
   </si>
   <si>
     <t xml:space="preserve">60 o más</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desde 60</t>
   </si>
 </sst>
 </file>
@@ -999,7 +996,7 @@
         <v>2022</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>12.61</v>
@@ -1010,7 +1007,7 @@
         <v>2023</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>12.26</v>
@@ -1021,7 +1018,7 @@
         <v>2024</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>11.1</v>

--- a/output/graficos_regionales_sexo_edad/plot_historia_nacional_o_ocup_a_2021_nacional.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_historia_nacional_o_ocup_a_2021_nacional.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 09:06</t>
+    <t xml:space="preserve">2026-10-05 04:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
